--- a/htr-Mapping-CDA-FHIR/ig/mappingPriseEnchargeCDAFHIR.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/mappingPriseEnchargeCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T13:48:36+00:00</t>
+    <t>2025-05-23T10:50:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/mappingPriseEnchargeCDAFHIR.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/mappingPriseEnchargeCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-23T10:50:09+00:00</t>
+    <t>2025-05-23T12:29:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
